--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -631,9 +631,18 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,44 +686,124 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>834</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>708</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -723,40 +812,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -765,40 +894,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -807,40 +976,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -849,40 +1058,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -891,40 +1140,80 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -933,40 +1222,80 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -975,40 +1304,80 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>546</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -631,7 +631,7 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -640,9 +640,18 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -726,84 +735,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>834</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>708</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -812,80 +901,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -894,80 +1023,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -976,80 +1145,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1058,80 +1267,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1140,80 +1389,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1222,80 +1511,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1304,80 +1633,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>545</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>546</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -631,7 +631,7 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -640,7 +640,7 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
@@ -649,9 +649,18 @@
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="3" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,124 +784,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>834</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -901,358 +990,406 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1262,231 +1399,279 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1506,241 +1691,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>606</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>523</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>545</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>0</t>
@@ -1750,6 +1983,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -640,7 +640,7 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
@@ -649,18 +649,9 @@
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -784,612 +775,484 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>834</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB3" t="n">
-        <v/>
-      </c>
-      <c r="AC3" t="n">
-        <v/>
-      </c>
-      <c r="AD3" t="n">
-        <v/>
-      </c>
-      <c r="AE3" t="n">
-        <v/>
-      </c>
-      <c r="AF3" t="n">
-        <v/>
-      </c>
-      <c r="AG3" t="n">
-        <v/>
-      </c>
-      <c r="AH3" t="n">
-        <v/>
-      </c>
-      <c r="AI3" t="n">
-        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB4" t="n">
-        <v/>
-      </c>
-      <c r="AC4" t="n">
-        <v/>
-      </c>
-      <c r="AD4" t="n">
-        <v/>
-      </c>
-      <c r="AE4" t="n">
-        <v/>
-      </c>
-      <c r="AF4" t="n">
-        <v/>
-      </c>
-      <c r="AG4" t="n">
-        <v/>
-      </c>
-      <c r="AH4" t="n">
-        <v/>
-      </c>
-      <c r="AI4" t="n">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1399,279 +1262,231 @@
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB5" t="n">
-        <v/>
-      </c>
-      <c r="AC5" t="n">
-        <v/>
-      </c>
-      <c r="AD5" t="n">
-        <v/>
-      </c>
-      <c r="AE5" t="n">
-        <v/>
-      </c>
-      <c r="AF5" t="n">
-        <v/>
-      </c>
-      <c r="AG5" t="n">
-        <v/>
-      </c>
-      <c r="AH5" t="n">
-        <v/>
-      </c>
-      <c r="AI5" t="n">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1691,289 +1506,241 @@
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>545</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>606</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>523</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>0</t>
@@ -1983,30 +1750,6 @@
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -631,27 +631,9 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="3" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,91 +677,11 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -813,86 +715,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -901,7 +723,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -935,86 +757,6 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1023,7 +765,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1057,86 +799,6 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1145,7 +807,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1179,86 +841,6 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1267,7 +849,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1282,7 +864,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>929</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1292,7 +874,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1301,86 +883,6 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1389,7 +891,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1404,17 +906,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1423,86 +925,6 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1511,7 +933,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1545,86 +967,6 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1633,7 +975,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1667,86 +1009,6 @@
         </is>
       </c>
       <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -634,6 +634,15 @@
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,44 +686,124 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -723,40 +812,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -765,40 +894,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -807,40 +976,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -849,40 +1058,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -891,40 +1140,80 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1495</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1495</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -933,40 +1222,80 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -975,40 +1304,80 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>545</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -631,7 +631,7 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -643,6 +643,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -726,84 +735,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -812,80 +901,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -894,80 +1023,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -976,80 +1145,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1058,80 +1267,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1140,80 +1389,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1495</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1495</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1222,80 +1511,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1304,80 +1633,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>545</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>545</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -631,7 +631,7 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -640,7 +640,7 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
@@ -652,6 +652,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,484 +784,612 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1262,241 +1399,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1616</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1435</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1495</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1495</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1506,241 +1691,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>546</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>545</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>0</t>
@@ -1750,6 +1983,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -640,7 +640,7 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
@@ -649,14 +649,14 @@
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
     <col width="5" customWidth="1" min="33" max="33"/>
     <col width="5" customWidth="1" min="34" max="34"/>
@@ -828,249 +828,249 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>prereg</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1136,87 +1136,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1282,87 +1282,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1428,87 +1428,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1574,112 +1574,112 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1611</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1616</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1435</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>166</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1495</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1720,87 +1720,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1866,112 +1866,112 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>546</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>546</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -634,6 +634,15 @@
     <col width="3" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,44 +686,124 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -723,40 +812,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -765,40 +894,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -807,40 +976,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -849,40 +1058,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -891,40 +1140,80 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1611</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -933,40 +1222,80 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -975,40 +1304,80 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>546</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -643,6 +643,15 @@
     <col width="3" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -726,84 +735,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -812,80 +901,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -894,80 +1023,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -976,80 +1145,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1058,80 +1267,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1140,80 +1389,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1560</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1611</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1222,80 +1511,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1304,80 +1633,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>546</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>546</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -779,87 +779,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -901,87 +901,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1023,87 +1023,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1145,87 +1145,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1267,87 +1267,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1389,112 +1389,112 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1560</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1560</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1511,87 +1511,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1633,87 +1633,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>545</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -630,7 +630,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -779,87 +779,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -901,87 +901,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1023,87 +1023,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1145,87 +1145,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1267,87 +1267,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1389,87 +1389,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1511,87 +1511,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1633,112 +1633,112 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>546</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>545</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -331,6 +331,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>176</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -623,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -640,18 +665,18 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="3" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,17 +889,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -884,17 +909,17 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -979,45 +1004,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="S3" t="n">
+        <v/>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
+      </c>
+      <c r="Z3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1101,45 +1110,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="S4" t="n">
+        <v/>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
+      </c>
+      <c r="Z4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1223,45 +1216,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1345,45 +1322,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1467,45 +1428,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1589,45 +1534,29 @@
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1711,45 +1640,119 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v/>
+      </c>
+      <c r="K10" t="n">
+        <v/>
+      </c>
+      <c r="L10" t="n">
+        <v/>
+      </c>
+      <c r="M10" t="n">
+        <v/>
+      </c>
+      <c r="N10" t="n">
+        <v/>
+      </c>
+      <c r="O10" t="n">
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v/>
+      </c>
+      <c r="Q10" t="n">
+        <v/>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -661,22 +661,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
     <col width="5" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -760,106 +751,66 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>dsl</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>230</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -874,50 +825,10 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -926,7 +837,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -964,75 +875,35 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v/>
-      </c>
-      <c r="T3" t="n">
-        <v/>
-      </c>
-      <c r="U3" t="n">
-        <v/>
-      </c>
-      <c r="V3" t="n">
-        <v/>
-      </c>
-      <c r="W3" t="n">
-        <v/>
-      </c>
-      <c r="X3" t="n">
-        <v/>
-      </c>
-      <c r="Y3" t="n">
-        <v/>
-      </c>
-      <c r="Z3" t="n">
+      <c r="J3" t="n">
+        <v/>
+      </c>
+      <c r="K3" t="n">
+        <v/>
+      </c>
+      <c r="L3" t="n">
+        <v/>
+      </c>
+      <c r="M3" t="n">
+        <v/>
+      </c>
+      <c r="N3" t="n">
+        <v/>
+      </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
+      <c r="Q3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1070,75 +941,35 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v/>
-      </c>
-      <c r="T4" t="n">
-        <v/>
-      </c>
-      <c r="U4" t="n">
-        <v/>
-      </c>
-      <c r="V4" t="n">
-        <v/>
-      </c>
-      <c r="W4" t="n">
-        <v/>
-      </c>
-      <c r="X4" t="n">
-        <v/>
-      </c>
-      <c r="Y4" t="n">
-        <v/>
-      </c>
-      <c r="Z4" t="n">
+      <c r="J4" t="n">
+        <v/>
+      </c>
+      <c r="K4" t="n">
+        <v/>
+      </c>
+      <c r="L4" t="n">
+        <v/>
+      </c>
+      <c r="M4" t="n">
+        <v/>
+      </c>
+      <c r="N4" t="n">
+        <v/>
+      </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
+      <c r="Q4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1176,75 +1007,35 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v/>
-      </c>
-      <c r="T5" t="n">
-        <v/>
-      </c>
-      <c r="U5" t="n">
-        <v/>
-      </c>
-      <c r="V5" t="n">
-        <v/>
-      </c>
-      <c r="W5" t="n">
-        <v/>
-      </c>
-      <c r="X5" t="n">
-        <v/>
-      </c>
-      <c r="Y5" t="n">
-        <v/>
-      </c>
-      <c r="Z5" t="n">
+      <c r="J5" t="n">
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v/>
+      </c>
+      <c r="N5" t="n">
+        <v/>
+      </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1259,7 +1050,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>929</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1269,7 +1060,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1282,75 +1073,35 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1388,75 +1139,35 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1494,75 +1205,35 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1577,7 +1248,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1587,7 +1258,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1600,158 +1271,28 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -331,31 +331,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>176</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="3810000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -654,20 +629,20 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -755,545 +730,641 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1557</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v/>
+      </c>
+      <c r="B9" t="n">
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v/>
+      </c>
+      <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v/>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,26 +623,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="3" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -726,84 +735,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -812,80 +901,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -894,80 +1023,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -976,80 +1145,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1058,80 +1267,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1140,80 +1389,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>892</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1557</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1222,146 +1511,226 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v/>
       </c>
-      <c r="B9" t="n">
+      <c r="K9" t="n">
         <v/>
       </c>
-      <c r="C9" t="n">
+      <c r="L9" t="n">
         <v/>
       </c>
-      <c r="D9" t="n">
+      <c r="M9" t="n">
         <v/>
       </c>
-      <c r="E9" t="n">
+      <c r="N9" t="n">
         <v/>
       </c>
-      <c r="F9" t="n">
+      <c r="O9" t="n">
         <v/>
       </c>
-      <c r="G9" t="n">
+      <c r="P9" t="n">
         <v/>
       </c>
-      <c r="H9" t="n">
+      <c r="Q9" t="n">
         <v/>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -631,27 +631,27 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,87 +779,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -901,87 +901,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1023,87 +1023,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1145,87 +1145,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1267,87 +1267,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1389,112 +1389,112 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1586</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1574</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1557</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>892</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1511,87 +1511,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1633,107 +1633,107 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
         <v/>
       </c>
-      <c r="K9" t="n">
+      <c r="T9" t="n">
         <v/>
       </c>
-      <c r="L9" t="n">
+      <c r="U9" t="n">
         <v/>
       </c>
-      <c r="M9" t="n">
+      <c r="V9" t="n">
         <v/>
       </c>
-      <c r="N9" t="n">
+      <c r="W9" t="n">
         <v/>
       </c>
-      <c r="O9" t="n">
+      <c r="X9" t="n">
         <v/>
       </c>
-      <c r="P9" t="n">
+      <c r="Y9" t="n">
         <v/>
       </c>
-      <c r="Q9" t="n">
+      <c r="Z9" t="n">
         <v/>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -640,18 +640,18 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,87 +779,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -901,87 +901,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1023,87 +1023,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1145,87 +1145,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1267,87 +1267,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1389,112 +1389,112 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1586</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1574</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1586</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1574</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1557</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>892</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1511,87 +1511,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1633,107 +1633,123 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -634,24 +634,6 @@
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,91 +677,11 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-April-2026</t>
+          <t>27-April-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -813,86 +715,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -901,7 +723,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24-April-2026</t>
+          <t>27-April-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -935,86 +757,6 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1023,7 +765,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-April-2026</t>
+          <t>27-April-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1057,86 +799,6 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1145,7 +807,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24-April-2026</t>
+          <t>27-April-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1179,86 +841,6 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1267,7 +849,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24-April-2026</t>
+          <t>27-April-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1301,86 +883,6 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1389,7 +891,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24-April-2026</t>
+          <t>27-April-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1399,12 +901,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1414,7 +916,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1423,86 +925,6 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1586</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1574</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1511,7 +933,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24-April-2026</t>
+          <t>27-April-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1545,86 +967,6 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1633,7 +975,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24-April-2026</t>
+          <t>27-April-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1648,7 +990,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1658,7 +1000,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1667,86 +1009,6 @@
         </is>
       </c>
       <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -631,9 +631,18 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,44 +686,124 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -723,40 +812,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -765,40 +894,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -807,40 +976,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -849,40 +1058,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -891,40 +1140,80 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1723</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1704</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -933,40 +1222,80 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -975,40 +1304,80 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -640,9 +640,18 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -726,84 +735,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -812,80 +901,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -894,80 +1023,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -976,80 +1145,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1058,80 +1267,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1140,80 +1389,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1723</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1718</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1723</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1704</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1222,80 +1511,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1304,80 +1633,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1121</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -649,9 +649,18 @@
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="3" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,484 +784,612 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>1717</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1262,241 +1399,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1723</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1718</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1723</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1718</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1506,241 +1691,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1121</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>0</t>
@@ -1750,6 +1983,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,10 +623,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -652,15 +652,6 @@
     <col width="3" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="6" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -784,612 +775,484 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>1717</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB3" t="n">
-        <v/>
-      </c>
-      <c r="AC3" t="n">
-        <v/>
-      </c>
-      <c r="AD3" t="n">
-        <v/>
-      </c>
-      <c r="AE3" t="n">
-        <v/>
-      </c>
-      <c r="AF3" t="n">
-        <v/>
-      </c>
-      <c r="AG3" t="n">
-        <v/>
-      </c>
-      <c r="AH3" t="n">
-        <v/>
-      </c>
-      <c r="AI3" t="n">
-        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB4" t="n">
-        <v/>
-      </c>
-      <c r="AC4" t="n">
-        <v/>
-      </c>
-      <c r="AD4" t="n">
-        <v/>
-      </c>
-      <c r="AE4" t="n">
-        <v/>
-      </c>
-      <c r="AF4" t="n">
-        <v/>
-      </c>
-      <c r="AG4" t="n">
-        <v/>
-      </c>
-      <c r="AH4" t="n">
-        <v/>
-      </c>
-      <c r="AI4" t="n">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1399,289 +1262,241 @@
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB5" t="n">
-        <v/>
-      </c>
-      <c r="AC5" t="n">
-        <v/>
-      </c>
-      <c r="AD5" t="n">
-        <v/>
-      </c>
-      <c r="AE5" t="n">
-        <v/>
-      </c>
-      <c r="AF5" t="n">
-        <v/>
-      </c>
-      <c r="AG5" t="n">
-        <v/>
-      </c>
-      <c r="AH5" t="n">
-        <v/>
-      </c>
-      <c r="AI5" t="n">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1723</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1718</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1691,289 +1506,241 @@
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1121</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>0</t>
@@ -1983,30 +1750,6 @@
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -634,24 +634,6 @@
     <col width="3" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="3" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,91 +677,11 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -813,86 +715,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -901,7 +723,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -935,86 +757,6 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1023,7 +765,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1057,86 +799,6 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1145,7 +807,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1179,86 +841,6 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1267,7 +849,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1301,86 +883,6 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1389,7 +891,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1423,86 +925,6 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1511,7 +933,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1545,86 +967,6 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1633,7 +975,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1648,7 +990,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1658,7 +1000,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1667,86 +1009,6 @@
         </is>
       </c>
       <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -634,6 +634,15 @@
     <col width="3" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,44 +686,124 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -723,40 +812,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -765,40 +894,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -807,40 +976,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -849,40 +1058,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -891,40 +1140,80 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -933,40 +1222,80 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -975,40 +1304,80 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1121</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -643,6 +643,15 @@
     <col width="3" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -726,84 +735,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -812,80 +901,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -894,80 +1023,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -976,80 +1145,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1058,80 +1267,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1140,80 +1389,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1222,80 +1511,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1304,80 +1633,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1121</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -779,87 +779,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -901,87 +901,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1023,87 +1023,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1145,87 +1145,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1267,87 +1267,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1389,87 +1389,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1511,87 +1511,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1633,112 +1633,112 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1121</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -629,11 +629,11 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -779,87 +779,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -901,87 +901,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1023,87 +1023,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1145,87 +1145,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1267,87 +1267,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1389,87 +1389,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1509,89 +1509,73 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v/>
+      </c>
+      <c r="B8" t="n">
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1631,114 +1615,98 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v/>
+      </c>
+      <c r="B9" t="n">
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v/>
+      </c>
+      <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v/>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1121</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1121</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,35 +623,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="3" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,91 +677,11 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -813,86 +715,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -901,22 +723,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>masterdata-ara</t>
+          <t>idrepo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>414</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -926,95 +748,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1023,12 +765,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>masterdata-eng</t>
+          <t>masterdata-ara</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1038,7 +780,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>929</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1053,90 +795,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1145,12 +807,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>masterdata-fra</t>
+          <t>masterdata-eng</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1160,7 +822,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1175,90 +837,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1267,120 +849,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>masterdata-fra</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>945</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>929</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1389,22 +891,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>prereg</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1419,302 +921,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v/>
-      </c>
-      <c r="B8" t="n">
-        <v/>
-      </c>
-      <c r="C8" t="n">
-        <v/>
-      </c>
-      <c r="D8" t="n">
-        <v/>
-      </c>
-      <c r="E8" t="n">
-        <v/>
-      </c>
-      <c r="F8" t="n">
-        <v/>
-      </c>
-      <c r="G8" t="n">
-        <v/>
-      </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v/>
-      </c>
-      <c r="B9" t="n">
-        <v/>
-      </c>
-      <c r="C9" t="n">
-        <v/>
-      </c>
-      <c r="D9" t="n">
-        <v/>
-      </c>
-      <c r="E9" t="n">
-        <v/>
-      </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
-      <c r="G9" t="n">
-        <v/>
-      </c>
-      <c r="H9" t="n">
-        <v/>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -634,6 +634,15 @@
     <col width="3" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,44 +686,124 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -723,40 +812,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -765,40 +894,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -807,40 +976,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -849,40 +1058,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -891,40 +1140,80 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -933,40 +1222,80 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -975,40 +1304,80 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -643,6 +643,15 @@
     <col width="3" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -726,84 +735,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -812,80 +901,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -894,80 +1023,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -976,80 +1145,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1058,80 +1267,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1140,80 +1389,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1222,80 +1511,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1304,80 +1633,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -631,7 +631,7 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -779,87 +779,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -901,87 +901,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1023,87 +1023,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1145,87 +1145,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1267,87 +1267,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1389,87 +1389,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1511,87 +1511,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1633,87 +1633,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -640,7 +640,7 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
@@ -779,87 +779,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -901,87 +901,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1023,87 +1023,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1145,87 +1145,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1267,87 +1267,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1389,87 +1389,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1787</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1485</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1472</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1511,87 +1511,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1633,112 +1633,112 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -634,24 +634,6 @@
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,91 +677,11 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -813,86 +715,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -901,7 +723,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -935,86 +757,6 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1023,7 +765,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1057,86 +799,6 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1145,7 +807,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1179,86 +841,6 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1267,7 +849,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1301,86 +883,6 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1389,7 +891,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1423,86 +925,6 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1511,7 +933,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1545,86 +967,6 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1633,7 +975,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1667,86 +1009,6 @@
         </is>
       </c>
       <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -634,6 +634,15 @@
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,44 +686,124 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -723,40 +812,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -765,40 +894,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -807,40 +976,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -849,40 +1058,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -891,40 +1140,80 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1787</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1787</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -933,40 +1222,80 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -975,40 +1304,80 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -631,7 +631,7 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -643,6 +643,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -726,84 +735,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -812,80 +901,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -894,80 +1023,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -976,80 +1145,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1058,80 +1267,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1140,80 +1389,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1787</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1787</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1222,80 +1511,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1304,80 +1633,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1123</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -640,7 +640,7 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
@@ -779,112 +779,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -901,87 +901,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1023,87 +1023,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1145,87 +1145,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1267,87 +1267,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1389,87 +1389,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1511,87 +1511,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1633,87 +1633,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa21.xlsx
+++ b/minio-report-tracker/xlxs/qa21.xlsx
@@ -331,6 +331,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>176</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -623,17 +648,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -648,10 +673,19 @@
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,484 +809,612 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1262,231 +1424,279 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1494,7 +1704,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1506,241 +1716,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1121</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>0</t>
@@ -1750,6 +2008,144 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v/>
+      </c>
+      <c r="B10" t="n">
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
+        <v/>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
